--- a/data/trans_orig/P1419-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1419-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2007</t>
+          <t>Población con diagnóstico de varices en las piernas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10872</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28025</t>
+          <t>28503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,57%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41084</t>
+          <t>41172</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>69621</t>
+          <t>68700</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56306</t>
+          <t>57650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90808</t>
+          <t>89877</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,5%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665987</t>
+          <t>665509</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>683140</t>
+          <t>682404</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,43%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>618730</t>
+          <t>619651</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>647267</t>
+          <t>647179</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>89,89%</t>
+          <t>90,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1291555</t>
+          <t>1292486</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1326057</t>
+          <t>1324713</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>95,83%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18536</t>
+          <t>18836</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40736</t>
+          <t>41364</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>85540</t>
+          <t>86598</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>126254</t>
+          <t>127069</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>113521</t>
+          <t>110550</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>159205</t>
+          <t>156757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>921064</t>
+          <t>920436</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>943264</t>
+          <t>942964</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,04%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>842139</t>
+          <t>841324</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>882853</t>
+          <t>881795</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,96%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1770988</t>
+          <t>1773436</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1816672</t>
+          <t>1819643</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,75%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,27%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14025</t>
+          <t>14121</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36153</t>
+          <t>34756</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63744</t>
+          <t>63858</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>96611</t>
+          <t>98138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,13%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81055</t>
+          <t>82931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>120000</t>
+          <t>119982</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>642356</t>
+          <t>643753</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664484</t>
+          <t>664388</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>587230</t>
+          <t>585703</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>620097</t>
+          <t>619983</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,87%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1242350</t>
+          <t>1242368</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1281295</t>
+          <t>1279419</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1622,7 +1622,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>93,91%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21523</t>
+          <t>20915</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41721</t>
+          <t>41817</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>107384</t>
+          <t>104461</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>146685</t>
+          <t>148635</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>14,31%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133235</t>
+          <t>134187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180427</t>
+          <t>180353</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>900501</t>
+          <t>900405</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>920699</t>
+          <t>921307</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>891927</t>
+          <t>889977</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>931228</t>
+          <t>934151</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,88%</t>
+          <t>85,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1800407</t>
+          <t>1800481</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1847599</t>
+          <t>1846647</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,89%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,23%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>82041</t>
+          <t>80228</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>118709</t>
+          <t>119234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>329617</t>
+          <t>331117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>402469</t>
+          <t>402712</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>422231</t>
+          <t>424119</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>507266</t>
+          <t>505612</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3157834</t>
+          <t>3157309</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3194502</t>
+          <t>3196315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2976728</t>
+          <t>2976485</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3049580</t>
+          <t>3048080</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,25%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6148475</t>
+          <t>6150129</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6233510</t>
+          <t>6231622</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,38%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2012</t>
+          <t>Población con diagnóstico de varices en las piernas en 2012 (tasa de respuesta: 99,97%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5350</t>
+          <t>5512</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20745</t>
+          <t>20749</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47326</t>
+          <t>46809</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77366</t>
+          <t>78321</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55337</t>
+          <t>58286</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>90955</t>
+          <t>92010</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>682724</t>
+          <t>682720</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>698119</t>
+          <t>697957</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,24%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>619684</t>
+          <t>618729</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>649724</t>
+          <t>650241</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,9%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,21%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1309564</t>
+          <t>1308509</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1345182</t>
+          <t>1342233</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,84%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5420</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19959</t>
+          <t>19246</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76968</t>
+          <t>74860</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113848</t>
+          <t>113533</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>85296</t>
+          <t>86720</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>125214</t>
+          <t>130197</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,36%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>997988</t>
+          <t>998701</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012480</t>
+          <t>1012527</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,46%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>915125</t>
+          <t>915440</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>952005</t>
+          <t>954113</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,94%</t>
+          <t>88,97%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1921707</t>
+          <t>1916724</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1961625</t>
+          <t>1960201</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,64%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,76%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3933</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>17036</t>
+          <t>16684</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>46429</t>
+          <t>45908</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78209</t>
+          <t>78449</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52848</t>
+          <t>54679</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>87949</t>
+          <t>89329</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,82%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740587</t>
+          <t>740939</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753690</t>
+          <t>753765</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,75%</t>
+          <t>97,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698965</t>
+          <t>698725</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>730745</t>
+          <t>731266</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1446848</t>
+          <t>1445468</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1481949</t>
+          <t>1480118</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,18%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,44%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4121</t>
+          <t>4956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19475</t>
+          <t>20067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66866</t>
+          <t>66631</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102185</t>
+          <t>101358</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75152</t>
+          <t>76142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>113777</t>
+          <t>114526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>928264</t>
+          <t>927672</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>943618</t>
+          <t>942783</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>949716</t>
+          <t>950543</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>985035</t>
+          <t>985270</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885863</t>
+          <t>1885114</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1924488</t>
+          <t>1923498</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,24%</t>
+          <t>96,19%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>29785</t>
+          <t>28211</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56192</t>
+          <t>56092</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>264972</t>
+          <t>268434</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>330767</t>
+          <t>337083</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>300661</t>
+          <t>301477</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>377543</t>
+          <t>376641</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,39%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3370587</t>
+          <t>3370687</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3396994</t>
+          <t>3398568</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3224331</t>
+          <t>3218015</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3290126</t>
+          <t>3286664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>92,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6604334</t>
+          <t>6605236</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6681216</t>
+          <t>6680400</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,61%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,69%</t>
+          <t>95,68%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2016</t>
+          <t>Población con diagnóstico de varices en las piernas en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4943</t>
+          <t>4603</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>18211</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>21477</t>
+          <t>20215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43876</t>
+          <t>42659</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28447</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>55490</t>
+          <t>53826</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656589</t>
+          <t>656853</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>669857</t>
+          <t>670197</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>628963</t>
+          <t>630180</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>651362</t>
+          <t>652624</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,48%</t>
+          <t>93,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>96,81%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1292149</t>
+          <t>1293813</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1319192</t>
+          <t>1318989</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,88%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,87%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4014</t>
+          <t>3981</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16170</t>
+          <t>16671</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59215</t>
+          <t>60338</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96243</t>
+          <t>97162</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>69821</t>
+          <t>68218</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108619</t>
+          <t>108377</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1006261</t>
+          <t>1005760</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018417</t>
+          <t>1018450</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,7 +5098,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>946670</t>
+          <t>945751</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>983698</t>
+          <t>982575</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,68%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1956725</t>
+          <t>1956967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1995523</t>
+          <t>1997126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,74%</t>
+          <t>94,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5987</t>
+          <t>6506</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19612</t>
+          <t>19385</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23195</t>
+          <t>23452</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>47838</t>
+          <t>45794</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>33895</t>
+          <t>31718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>59279</t>
+          <t>60141</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>739940</t>
+          <t>740167</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753565</t>
+          <t>753046</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>737173</t>
+          <t>739217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>761816</t>
+          <t>761559</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1485284</t>
+          <t>1484422</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1510668</t>
+          <t>1512845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13570</t>
+          <t>13952</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34064</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59600</t>
+          <t>59807</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97140</t>
+          <t>95692</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>78164</t>
+          <t>80582</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>121297</t>
+          <t>120609</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,09%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>903503</t>
+          <t>903325</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923997</t>
+          <t>923615</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,51%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>946639</t>
+          <t>948087</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>984179</t>
+          <t>983972</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,69%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1860049</t>
+          <t>1860737</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1903182</t>
+          <t>1900764</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,06%</t>
+          <t>95,93%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39669</t>
+          <t>39723</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>68983</t>
+          <t>66907</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>190504</t>
+          <t>187489</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>250283</t>
+          <t>251019</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238736</t>
+          <t>238950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>304018</t>
+          <t>307574</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,43%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3325367</t>
+          <t>3327443</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3354681</t>
+          <t>3354627</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,7 +6127,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3294259</t>
+          <t>3293523</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3354038</t>
+          <t>3357053</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,94%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,63%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6634874</t>
+          <t>6631318</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6700156</t>
+          <t>6699942</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de varices en las piernas en 2023</t>
+          <t>Población con diagnóstico de varices en las piernas en 2023 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16498</t>
+          <t>16326</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36251</t>
+          <t>35376</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68106</t>
+          <t>68144</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92390</t>
+          <t>92828</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,74%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>90729</t>
+          <t>89986</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>122289</t>
+          <t>121453</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,27%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>599190</t>
+          <t>600065</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>618943</t>
+          <t>619115</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,3%</t>
+          <t>94,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>582980</t>
+          <t>582542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>607264</t>
+          <t>607226</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,32%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,92%</t>
+          <t>89,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1188522</t>
+          <t>1189358</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1220082</t>
+          <t>1220825</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,67%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>93,14%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13603</t>
+          <t>13392</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40322</t>
+          <t>40685</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>89696</t>
+          <t>90177</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118244</t>
+          <t>118930</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86318</t>
+          <t>83522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156768</t>
+          <t>156267</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1152542</t>
+          <t>1152179</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1179261</t>
+          <t>1179472</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,59%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>838470</t>
+          <t>837784</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>867018</t>
+          <t>866537</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,64%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,62%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1992810</t>
+          <t>1993311</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2063260</t>
+          <t>2066056</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,71%</t>
+          <t>92,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>96,11%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>22062</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>41344</t>
+          <t>43510</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38684</t>
+          <t>37201</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108727</t>
+          <t>108701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7310,7 +7310,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65329</t>
+          <t>71350</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>132088</t>
+          <t>131814</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,06%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>661621</t>
+          <t>659455</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>682386</t>
+          <t>680903</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>824479</t>
+          <t>824505</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>894522</t>
+          <t>896005</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>96,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1504083</t>
+          <t>1504357</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1570842</t>
+          <t>1564821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>91,94%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,64%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30641</t>
+          <t>29087</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53165</t>
+          <t>51860</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>81051</t>
+          <t>82839</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121718</t>
+          <t>121459</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>123718</t>
+          <t>122573</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165801</t>
+          <t>165253</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,19%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>873666</t>
+          <t>874971</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>896190</t>
+          <t>897744</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>970196</t>
+          <t>970455</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1010863</t>
+          <t>1009075</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,58%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1852944</t>
+          <t>1853492</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1895027</t>
+          <t>1896172</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,79%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,87%</t>
+          <t>93,93%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>94642</t>
+          <t>93768</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>145440</t>
+          <t>145705</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,7 +7961,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>303230</t>
+          <t>301167</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>405612</t>
+          <t>407814</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>8,23%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>427074</t>
+          <t>428811</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>534207</t>
+          <t>538558</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3312661</t>
+          <t>3312396</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3363459</t>
+          <t>3364333</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8079,7 +8079,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3251592</t>
+          <t>3249390</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3353974</t>
+          <t>3356037</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,91%</t>
+          <t>88,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,71%</t>
+          <t>91,77%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6581099</t>
+          <t>6576748</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6688232</t>
+          <t>6686495</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>94,0%</t>
+          <t>93,97%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1419-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P1419-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>11608</t>
+          <t>11696</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28503</t>
+          <t>28668</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,67%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>41172</t>
+          <t>40718</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>68700</t>
+          <t>68548</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>57650</t>
+          <t>59209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>89877</t>
+          <t>91731</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,28%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,64%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>665509</t>
+          <t>665344</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>682404</t>
+          <t>682316</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,33%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>619651</t>
+          <t>619803</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>647179</t>
+          <t>647633</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>90,02%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1292486</t>
+          <t>1290632</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1324713</t>
+          <t>1323154</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,72%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18836</t>
+          <t>18306</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41364</t>
+          <t>41791</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>86598</t>
+          <t>85060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>127069</t>
+          <t>126799</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>110550</t>
+          <t>112593</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156757</t>
+          <t>158224</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>920436</t>
+          <t>920009</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>942964</t>
+          <t>943494</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>841324</t>
+          <t>841594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>881795</t>
+          <t>883333</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,88%</t>
+          <t>86,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1773436</t>
+          <t>1771969</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1819643</t>
+          <t>1817600</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,17%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14121</t>
+          <t>14089</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>34756</t>
+          <t>33566</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63858</t>
+          <t>62223</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>98138</t>
+          <t>95915</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>82931</t>
+          <t>81385</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>119982</t>
+          <t>120850</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,87%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>643753</t>
+          <t>644943</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>664388</t>
+          <t>664420</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>585703</t>
+          <t>587926</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>619983</t>
+          <t>621618</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1242368</t>
+          <t>1241500</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1279419</t>
+          <t>1280965</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,19%</t>
+          <t>91,13%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20915</t>
+          <t>21742</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41817</t>
+          <t>42912</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104461</t>
+          <t>106201</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>148635</t>
+          <t>149226</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,37%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134187</t>
+          <t>133142</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>180353</t>
+          <t>183007</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>900405</t>
+          <t>899310</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>921307</t>
+          <t>920480</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>95,56%</t>
+          <t>95,45%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>889977</t>
+          <t>889386</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>934151</t>
+          <t>932411</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>89,94%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1800481</t>
+          <t>1797827</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1846647</t>
+          <t>1847692</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>90,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,23%</t>
+          <t>93,28%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>80228</t>
+          <t>79996</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119234</t>
+          <t>120579</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>331117</t>
+          <t>326983</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>402712</t>
+          <t>400540</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>424119</t>
+          <t>419464</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>505612</t>
+          <t>503578</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3157309</t>
+          <t>3155964</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3196315</t>
+          <t>3196547</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2976485</t>
+          <t>2978657</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3048080</t>
+          <t>3052214</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,08%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,32%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6150129</t>
+          <t>6152163</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6231622</t>
+          <t>6236277</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,7%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5512</t>
+          <t>5859</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>20749</t>
+          <t>22064</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46809</t>
+          <t>45761</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78321</t>
+          <t>77109</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>58286</t>
+          <t>57837</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>92010</t>
+          <t>91569</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,54%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>682720</t>
+          <t>681405</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>697957</t>
+          <t>697610</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>618729</t>
+          <t>619941</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>650241</t>
+          <t>651289</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,94%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1308509</t>
+          <t>1308950</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1342233</t>
+          <t>1342682</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,87%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5420</t>
+          <t>5686</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>19246</t>
+          <t>19612</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74860</t>
+          <t>74380</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>113533</t>
+          <t>113643</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>86720</t>
+          <t>87494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130197</t>
+          <t>129658</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>6,36%</t>
+          <t>6,33%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>998701</t>
+          <t>998335</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1012527</t>
+          <t>1012261</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,11%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>915440</t>
+          <t>915330</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>954113</t>
+          <t>954593</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>88,97%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1916724</t>
+          <t>1917263</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1960201</t>
+          <t>1959427</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>93,64%</t>
+          <t>93,67%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,76%</t>
+          <t>95,73%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3858</t>
+          <t>3080</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>16684</t>
+          <t>17453</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>45908</t>
+          <t>46236</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>78449</t>
+          <t>78936</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54679</t>
+          <t>54159</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89329</t>
+          <t>88705</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740939</t>
+          <t>740170</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753765</t>
+          <t>754543</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>698725</t>
+          <t>698238</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>731266</t>
+          <t>730938</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>89,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,05%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1445468</t>
+          <t>1446092</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1480118</t>
+          <t>1480638</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>96,44%</t>
+          <t>96,47%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4956</t>
+          <t>5004</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>20067</t>
+          <t>19675</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>66631</t>
+          <t>67752</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101358</t>
+          <t>102424</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,74%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76142</t>
+          <t>74832</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>114526</t>
+          <t>112653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,63%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>927672</t>
+          <t>928064</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>942783</t>
+          <t>942735</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,48%</t>
+          <t>99,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>950543</t>
+          <t>949477</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>985270</t>
+          <t>984149</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1885114</t>
+          <t>1886987</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1923498</t>
+          <t>1924808</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,26%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>28211</t>
+          <t>29023</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56092</t>
+          <t>57158</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>268434</t>
+          <t>268396</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>337083</t>
+          <t>331839</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>301477</t>
+          <t>306249</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>376641</t>
+          <t>379222</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3370687</t>
+          <t>3369621</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3398568</t>
+          <t>3397756</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3218015</t>
+          <t>3223259</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3286664</t>
+          <t>3286702</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6605236</t>
+          <t>6602655</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6680400</t>
+          <t>6675628</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,61%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,61%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4603</t>
+          <t>4739</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>17585</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>20215</t>
+          <t>20649</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42659</t>
+          <t>43301</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28650</t>
+          <t>29270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>53826</t>
+          <t>54932</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>656853</t>
+          <t>657215</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>670197</t>
+          <t>670061</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>630180</t>
+          <t>629538</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>652624</t>
+          <t>652190</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,66%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1293813</t>
+          <t>1292707</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1318989</t>
+          <t>1318369</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,87%</t>
+          <t>97,83%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4081</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16671</t>
+          <t>15807</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>60338</t>
+          <t>60942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>97162</t>
+          <t>97898</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>68218</t>
+          <t>66559</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>108377</t>
+          <t>110862</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,37%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1005760</t>
+          <t>1006624</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1018450</t>
+          <t>1018350</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>945751</t>
+          <t>945015</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>982575</t>
+          <t>981971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>90,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,21%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1956967</t>
+          <t>1954482</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1997126</t>
+          <t>1998785</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,75%</t>
+          <t>94,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,78%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>6506</t>
+          <t>6478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>19385</t>
+          <t>20214</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>23452</t>
+          <t>23544</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>45794</t>
+          <t>48398</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31718</t>
+          <t>32573</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>60141</t>
+          <t>60712</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,93%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>740167</t>
+          <t>739338</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>753046</t>
+          <t>753074</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,15%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>739217</t>
+          <t>736613</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>761559</t>
+          <t>761467</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,01%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1484422</t>
+          <t>1483851</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1512845</t>
+          <t>1511990</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>14301</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34242</t>
+          <t>34693</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59807</t>
+          <t>61007</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95692</t>
+          <t>96939</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>80582</t>
+          <t>78929</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120609</t>
+          <t>122622</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,19%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>903325</t>
+          <t>902874</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>923615</t>
+          <t>923266</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,47%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>948087</t>
+          <t>946840</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>983972</t>
+          <t>982772</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1860737</t>
+          <t>1858724</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1900764</t>
+          <t>1902417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,93%</t>
+          <t>96,02%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>39723</t>
+          <t>39141</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>66907</t>
+          <t>69582</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>187489</t>
+          <t>189281</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>251019</t>
+          <t>249845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>238950</t>
+          <t>235967</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>307574</t>
+          <t>305143</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3327443</t>
+          <t>3324768</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3354627</t>
+          <t>3355209</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3293523</t>
+          <t>3294697</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3357053</t>
+          <t>3355261</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6631318</t>
+          <t>6633749</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6699942</t>
+          <t>6702925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,57%</t>
+          <t>95,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,56%</t>
+          <t>96,6%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>24473</t>
+          <t>27040</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16326</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35376</t>
+          <t>39116</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>79518</t>
+          <t>85014</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68144</t>
+          <t>71897</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>92828</t>
+          <t>99965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>103991</t>
+          <t>112054</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>89986</t>
+          <t>96108</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>121453</t>
+          <t>130533</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>610968</t>
+          <t>663670</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>600065</t>
+          <t>651594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>619115</t>
+          <t>672550</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>96,15%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>595852</t>
+          <t>647708</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>582542</t>
+          <t>632757</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>607226</t>
+          <t>660825</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>88,23%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,19%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1206820</t>
+          <t>1311377</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1189358</t>
+          <t>1292898</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1220825</t>
+          <t>1327323</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,13%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1310811</t>
+          <t>1423431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27534</t>
+          <t>31516</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13392</t>
+          <t>22605</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40685</t>
+          <t>43504</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>103913</t>
+          <t>114014</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90177</t>
+          <t>99087</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>118930</t>
+          <t>130494</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>131447</t>
+          <t>145529</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83522</t>
+          <t>128121</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>156267</t>
+          <t>166612</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1165330</t>
+          <t>1017401</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1152179</t>
+          <t>1005413</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1179472</t>
+          <t>1026312</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>96,59%</t>
+          <t>95,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>97,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>852801</t>
+          <t>955470</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>837784</t>
+          <t>938990</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>866537</t>
+          <t>970397</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,14%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>87,57%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,74%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>2018131</t>
+          <t>1972872</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1993311</t>
+          <t>1951789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2066056</t>
+          <t>1990280</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,14%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>93,95%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>956714</t>
+          <t>1069484</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>956714</t>
+          <t>1069484</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>956714</t>
+          <t>1069484</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2149578</t>
+          <t>2118401</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2149578</t>
+          <t>2118401</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2149578</t>
+          <t>2118401</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>30118</t>
+          <t>35840</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>22062</t>
+          <t>25789</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>43510</t>
+          <t>49000</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>79102</t>
+          <t>93696</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37201</t>
+          <t>78297</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>108701</t>
+          <t>108403</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>109220</t>
+          <t>129536</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71350</t>
+          <t>112143</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>131814</t>
+          <t>150881</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>672847</t>
+          <t>765377</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>659455</t>
+          <t>752217</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>680903</t>
+          <t>775428</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>95,53%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>854104</t>
+          <t>717880</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>824505</t>
+          <t>703173</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>896005</t>
+          <t>733279</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,52%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,35%</t>
+          <t>86,64%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1526951</t>
+          <t>1483257</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1504357</t>
+          <t>1461912</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1564821</t>
+          <t>1500650</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>91,94%</t>
+          <t>90,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>93,05%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>702965</t>
+          <t>801217</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>933206</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>933206</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>933206</t>
+          <t>811576</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1636171</t>
+          <t>1612793</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1636171</t>
+          <t>1612793</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1636171</t>
+          <t>1612793</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>39748</t>
+          <t>40864</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>29087</t>
+          <t>29083</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>51860</t>
+          <t>52439</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>103843</t>
+          <t>113612</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>82839</t>
+          <t>99226</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121459</t>
+          <t>132558</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>143591</t>
+          <t>154476</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>122573</t>
+          <t>135159</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165253</t>
+          <t>175135</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>8,31%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>887083</t>
+          <t>949198</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>874971</t>
+          <t>937623</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>897744</t>
+          <t>960979</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,71%</t>
+          <t>95,87%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>988071</t>
+          <t>1004022</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>970455</t>
+          <t>985076</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>1009075</t>
+          <t>1018408</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>88,88%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1875154</t>
+          <t>1953220</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1853492</t>
+          <t>1932561</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1896172</t>
+          <t>1972537</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,81%</t>
+          <t>91,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,93%</t>
+          <t>93,59%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1091914</t>
+          <t>1117634</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2018745</t>
+          <t>2107696</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>121874</t>
+          <t>135259</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>93768</t>
+          <t>115239</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>145705</t>
+          <t>157044</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>366375</t>
+          <t>406336</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>301167</t>
+          <t>379438</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>407814</t>
+          <t>439184</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>10,02%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>488249</t>
+          <t>541595</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>428811</t>
+          <t>501568</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>538558</t>
+          <t>578599</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3336227</t>
+          <t>3395647</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3312396</t>
+          <t>3373862</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3364333</t>
+          <t>3415667</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,74%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3290829</t>
+          <t>3325079</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3249390</t>
+          <t>3292231</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3356037</t>
+          <t>3351977</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>89,98%</t>
+          <t>89,11%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>88,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>91,77%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6627057</t>
+          <t>6720727</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6576748</t>
+          <t>6683723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6686495</t>
+          <t>6760754</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>92,54%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,43%</t>
+          <t>92,03%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3458101</t>
+          <t>3530906</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3458101</t>
+          <t>3530906</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3458101</t>
+          <t>3530906</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3657204</t>
+          <t>3731415</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3657204</t>
+          <t>3731415</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3657204</t>
+          <t>3731415</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7115306</t>
+          <t>7262322</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7115306</t>
+          <t>7262322</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7115306</t>
+          <t>7262322</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
